--- a/doc/source/_static/data/economy/sector-correspondence.xlsx
+++ b/doc/source/_static/data/economy/sector-correspondence.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXIOBASE industries" sheetId="1" r:id="R884942a0f83c45bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXIOBASE products" sheetId="2" r:id="R351f91f7ca3742c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXIOBASE Hybrid activities" sheetId="3" r:id="R6554bbcc825744ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXIOBASE Hybrid products" sheetId="4" r:id="R4d70a75153c74fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OECD ICIO" sheetId="5" r:id="R1049df862c794ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADB" sheetId="6" r:id="R76c161875e824630"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIOD industries" sheetId="7" r:id="R8ba072535fba457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WIOD activities" sheetId="8" r:id="Ra56a63294e284005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIGARO activities" sheetId="9" r:id="Ra707f77a67234d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIGARO products" sheetId="10" r:id="R9250d34620ab460e"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="EXIOBASE industries" sheetId="1" r:id="R884942a0f83c45bf"/>
+    <sheet name="EXIOBASE products" sheetId="2" r:id="R351f91f7ca3742c7"/>
+    <sheet name="EXIOBASE Hybrid activities" sheetId="3" r:id="R6554bbcc825744ce"/>
+    <sheet name="EXIOBASE Hybrid products" sheetId="4" r:id="R4d70a75153c74fd7"/>
+    <sheet name="OECD ICIO" sheetId="5" r:id="R1049df862c794ab5"/>
+    <sheet name="ADB" sheetId="6" r:id="R76c161875e824630"/>
+    <sheet name="WIOD industries" sheetId="7" r:id="R8ba072535fba457f"/>
+    <sheet name="WIOD activities" sheetId="8" r:id="Ra56a63294e284005"/>
+    <sheet name="FIGARO activities" sheetId="9" r:id="Ra707f77a67234d8a"/>
+    <sheet name="FIGARO products" sheetId="10" r:id="R9250d34620ab460e"/>
+    <sheet name="Read me" sheetId="11" r:id="rId1"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21,106 +22,167 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
-    <x:numFmt numFmtId="200" formatCode="@"/>
-    <x:numFmt numFmtId="201" formatCode="0"/>
-  </x:numFmts>
-  <x:fonts count="5">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="14"/>
-      <x:color rgb="FF202C38"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF566675"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF202C38"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF245B6A"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="2">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom style="thin">
-        <x:color rgb="FF245B6A"/>
-      </x:bottom>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="13">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="200" formatCode="@"/>
+    <numFmt numFmtId="201" formatCode="0"/>
+    <numFmt numFmtId="202" formatCode="@"/>
+  </numFmts>
+  <fonts count="9">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF202C38"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF566675"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202C38"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+  </fonts>
+  <fills count="6">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF245B6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF302820"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF245B6A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2"/>
+  </cellStyleXfs>
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="202" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18554,4 +18616,220 @@
     <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb07236ef1fd4a25"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/source_notice11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFF0783C"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <c r="A1" s="19" t="str">
+        <v>Read me</v>
+      </c>
+      <c r="B1" s="19" t="str">
+        <v>Native sector aggregates for the indicator browser</v>
+      </c>
+    </row>
+    <row r="2" ht="24" hidden="0" customHeight="1">
+      <c r="A2" s="17" t="str">
+        <v>Contents</v>
+      </c>
+      <c r="B2" s="20" t="str">
+        <v>Native categories assigned once to broad source-classification sections. This is the indicator aggregation mapping, not the fine NACE Rev. 2.1 / CPA 2.2 concordance.</v>
+      </c>
+    </row>
+    <row r="3" ht="15" hidden="0" customHeight="1">
+      <c r="A3" s="17" t="str">
+        <v>How to use</v>
+      </c>
+      <c r="B3" s="20" t="str">
+        <v>Read the column labels and the notes on each sheet. Preserve native codes as text.</v>
+      </c>
+    </row>
+    <row r="4" ht="15" hidden="0" customHeight="1">
+      <c r="A4" s="17" t="str">
+        <v>Source</v>
+      </c>
+      <c r="B4" s="20" t="str">
+        <v>https://github.com/it-is-me-mario/MARIO</v>
+      </c>
+    </row>
+    <row r="5" ht="15" hidden="0" customHeight="1">
+      <c r="A5" s="17" t="str">
+        <v>Attribution</v>
+      </c>
+      <c r="B5" s="20" t="str">
+        <v>MARIO documentation; source publishers listed on the individual sheets.</v>
+      </c>
+    </row>
+    <row r="6" ht="24" hidden="0" customHeight="1">
+      <c r="A6" s="17" t="str">
+        <v>Reuse</v>
+      </c>
+      <c r="B6" s="20" t="str">
+        <v>MARIO example code follows GPL-3.0. Third-party classification records retain their source-specific rights; this workbook has no blanket licence replacing those terms.</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="0" customHeight="1">
+      <c r="A7" s="17" t="str">
+        <v>Licence URL</v>
+      </c>
+      <c r="B7" s="20" t="str">
+        <v>https://github.com/it-is-me-mario/MARIO/blob/main/LICENSE</v>
+      </c>
+    </row>
+    <row r="8" ht="24" hidden="0" customHeight="1">
+      <c r="A8" s="17" t="str">
+        <v>Limit</v>
+      </c>
+      <c r="B8" s="20" t="str">
+        <v>Section letters from different classification revisions are not directly interchangeable. Use classification-concordances.xlsx for qualified fine-code lookups. No numerical split weights are inferred.</v>
+      </c>
+    </row>
+    <row r="9" ht="15" hidden="0" customHeight="1">
+      <c r="A9" s="17" t="str">
+        <v>adb source</v>
+      </c>
+      <c r="B9" s="20" t="str">
+        <v>https://www.adb.org/what-we-do/data/regional-input-output-tables · ADB Key Indicators data terms · https://kidb.adb.org/terms</v>
+      </c>
+    </row>
+    <row r="10" ht="15" hidden="0" customHeight="1">
+      <c r="A10" s="17" t="str">
+        <v>emerging source</v>
+      </c>
+      <c r="B10" s="20" t="str">
+        <v>https://zenodo.org/records/10956623 · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="11" ht="15" hidden="0" customHeight="1">
+      <c r="A11" s="17" t="str">
+        <v>emerging source</v>
+      </c>
+      <c r="B11" s="20" t="str">
+        <v>https://zenodo.org/records/17557778 · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="12" ht="15" hidden="0" customHeight="1">
+      <c r="A12" s="17" t="str">
+        <v>emerging source</v>
+      </c>
+      <c r="B12" s="20" t="str">
+        <v>https://zenodo.org/records/19461860 · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="13" ht="15" hidden="0" customHeight="1">
+      <c r="A13" s="17" t="str">
+        <v>emerging source</v>
+      </c>
+      <c r="B13" s="20" t="str">
+        <v>https://zenodo.org/records/18303090 · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="14" ht="15" hidden="0" customHeight="1">
+      <c r="A14" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B14" s="20" t="str">
+        <v>https://zenodo.org/records/18937492 · Custom non-commercial licence · https://zenodo.org/records/18937492</v>
+      </c>
+    </row>
+    <row r="15" ht="15" hidden="0" customHeight="1">
+      <c r="A15" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B15" s="20" t="str">
+        <v>https://zenodo.org/records/20051562 · Custom non-commercial licence · https://zenodo.org/records/20051562</v>
+      </c>
+    </row>
+    <row r="16" ht="15" hidden="0" customHeight="1">
+      <c r="A16" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B16" s="20" t="str">
+        <v>https://zenodo.org/records/23039074 · Custom non-commercial licence · https://zenodo.org/records/23039074</v>
+      </c>
+    </row>
+    <row r="17" ht="15" hidden="0" customHeight="1">
+      <c r="A17" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B17" s="20" t="str">
+        <v>https://zenodo.org/records/5589597 · CC BY-SA 4.0 · https://creativecommons.org/licenses/by-sa/4.0/</v>
+      </c>
+    </row>
+    <row r="18" ht="15" hidden="0" customHeight="1">
+      <c r="A18" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B18" s="20" t="str">
+        <v>https://zenodo.org/records/14614930 · Custom non-commercial licence · https://zenodo.org/records/14614930</v>
+      </c>
+    </row>
+    <row r="19" ht="15" hidden="0" customHeight="1">
+      <c r="A19" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B19" s="20" t="str">
+        <v>https://zenodo.org/records/14869924 · Custom non-commercial licence · https://zenodo.org/records/14869924</v>
+      </c>
+    </row>
+    <row r="20" ht="15" hidden="0" customHeight="1">
+      <c r="A20" s="17" t="str">
+        <v>exiobase-monetary source</v>
+      </c>
+      <c r="B20" s="20" t="str">
+        <v>https://zenodo.org/records/15689391 · Custom non-commercial licence · https://zenodo.org/records/15689391</v>
+      </c>
+    </row>
+    <row r="21" ht="15" hidden="0" customHeight="1">
+      <c r="A21" s="17" t="str">
+        <v>exiobase-hybrid source</v>
+      </c>
+      <c r="B21" s="20" t="str">
+        <v>https://zenodo.org/records/7244919 · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+    <row r="22" ht="24" hidden="0" customHeight="1">
+      <c r="A22" s="17" t="str">
+        <v>figaro source</v>
+      </c>
+      <c r="B22" s="20" t="str">
+        <v>https://ec.europa.eu/eurostat/web/esa-supply-use-input-tables/database · Eurostat data reuse policy · https://ec.europa.eu/eurostat/help/copyright-notice</v>
+      </c>
+    </row>
+    <row r="23" ht="15" hidden="0" customHeight="1">
+      <c r="A23" s="17" t="str">
+        <v>gloria source</v>
+      </c>
+      <c r="B23" s="20" t="str">
+        <v>https://ielab.info/resources/gloria · CC BY-NC 3.0 Australia · https://creativecommons.org/licenses/by-nc/3.0/au/</v>
+      </c>
+    </row>
+    <row r="24" ht="24" hidden="0" customHeight="1">
+      <c r="A24" s="17" t="str">
+        <v>oecd source</v>
+      </c>
+      <c r="B24" s="20" t="str">
+        <v>https://www.oecd.org/en/data/datasets/inter-country-input-output-tables.html · OECD Data terms · https://www.oecd.org/en/about/terms-conditions.html#data</v>
+      </c>
+    </row>
+    <row r="25" ht="15" hidden="0" customHeight="1">
+      <c r="A25" s="17" t="str">
+        <v>wiod source</v>
+      </c>
+      <c r="B25" s="20" t="str">
+        <v>https://www.rug.nl/ggdc/valuechain/wiod/wiod-2016-release?lang=en · CC BY 4.0 · https://creativecommons.org/licenses/by/4.0/</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>